--- a/06_Marketing_and_Feasibility_Study/دراسة_الجدوى_الاقتصادية_والخطة_التسويقية.xlsx
+++ b/06_Marketing_and_Feasibility_Study/دراسة_الجدوى_الاقتصادية_والخطة_التسويقية.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="المقارنة المالية والوفورات" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="جدوى المواسم والوفر المالي" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="مقارنة منصات التسويق" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -12,42 +12,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>📊 دراسة الجدوى الاقتصادية والمقارنة المالية — فندق هينو الأهرامات (الحجز المباشر vs عمولات OTAs)</t>
-  </si>
-  <si>
-    <t>نسبة الإشغال</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+  <si>
+    <t>📊 دراسة الجدوى الموسمية — فندق هينو الأهرامات ($15 Low Season vs $25 High Season)</t>
+  </si>
+  <si>
+    <t>الموسم ونسبة الإشغال</t>
+  </si>
+  <si>
+    <t>متوسط سعر الليلة (ADR)</t>
   </si>
   <si>
     <t>الليالي المشغولة / شهر</t>
   </si>
   <si>
-    <t>إجمالي الإيرادات (ADR = 2,500 جـ)</t>
-  </si>
-  <si>
-    <t>تكلفة عمولة OTAs التقليدية (35%)</t>
-  </si>
-  <si>
-    <t>تكلفة الحملة المباشرة (جوجل ماب 15 ألف + الموقع)</t>
-  </si>
-  <si>
-    <t>عمولة المنصات الثانوية Agoda/Airbnb (15% على 30%)</t>
-  </si>
-  <si>
-    <t>إجمالي تكلفة القناة الجديدة</t>
+    <t>إجمالي الإيرادات الشهرية</t>
+  </si>
+  <si>
+    <t>عمولات OTAs التقليدية (35%)</t>
+  </si>
+  <si>
+    <t>تكلفة حملة جوجل والموقع (17.1k)</t>
+  </si>
+  <si>
+    <t>عمولة Agoda/Airbnb (15% على 30%)</t>
+  </si>
+  <si>
+    <t>إجمالي تكلفة القناة المباشرة</t>
   </si>
   <si>
     <t>صافي الوفر الشهري لصالح الفندق</t>
   </si>
   <si>
-    <t>إشغال منخفض (50%)</t>
-  </si>
-  <si>
-    <t>إشغال متوسط (70%)</t>
-  </si>
-  <si>
-    <t>إشغال مرتفع (85%)</t>
+    <t>Low Season (إشغال 50%)</t>
+  </si>
+  <si>
+    <t>$15 (750 جـ)</t>
+  </si>
+  <si>
+    <t>Low Season (إشغال 70%)</t>
+  </si>
+  <si>
+    <t>High Season (إشغال 70%)</t>
+  </si>
+  <si>
+    <t>$25 (1,250 جـ)</t>
+  </si>
+  <si>
+    <t>High Season (إشغال 85%)</t>
   </si>
   <si>
     <t>🔍 مقارنة الجدوى التسويقية والتحويل (Google Maps vs Meta Facebook/Instagram)</t>
@@ -565,19 +577,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -588,8 +601,9 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="3" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="3" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -614,100 +628,149 @@
       <c r="H3" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4">
         <v>375</v>
       </c>
-      <c r="C4" s="4">
-        <v>937500</v>
-      </c>
       <c r="D4" s="4">
-        <f>C4*0.35</f>
-        <v>328125</v>
+        <f>C4*750</f>
+        <v>281250</v>
       </c>
       <c r="E4" s="4">
+        <f>D4*0.35</f>
+        <v>98437.5</v>
+      </c>
+      <c r="F4" s="4">
         <v>17083</v>
       </c>
-      <c r="F4" s="4">
-        <f>C4*0.30*0.15</f>
-        <v>42187.5</v>
-      </c>
       <c r="G4" s="4">
-        <f>E4+F4</f>
-        <v>59270.5</v>
+        <f>D4*0.30*0.15</f>
+        <v>12656.25</v>
       </c>
       <c r="H4" s="4">
-        <f>D4-G4</f>
-        <v>268854.5</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <f>F4+G4</f>
+        <v>29739.25</v>
+      </c>
+      <c r="I4" s="4">
+        <f>E4-H4</f>
+        <v>68698.25</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="4">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4">
         <v>525</v>
       </c>
-      <c r="C5" s="4">
-        <v>1312500</v>
-      </c>
       <c r="D5" s="4">
-        <f>C5*0.35</f>
-        <v>459375</v>
+        <f>C5*750</f>
+        <v>393750</v>
       </c>
       <c r="E5" s="4">
+        <f>D5*0.35</f>
+        <v>137812.5</v>
+      </c>
+      <c r="F5" s="4">
         <v>17083</v>
       </c>
-      <c r="F5" s="4">
-        <f>C5*0.30*0.15</f>
-        <v>59062.5</v>
-      </c>
       <c r="G5" s="4">
-        <f>E5+F5</f>
-        <v>76145.5</v>
+        <f>D5*0.30*0.15</f>
+        <v>17718.75</v>
       </c>
       <c r="H5" s="4">
-        <f>D5-G5</f>
-        <v>383229.5</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <f>F5+G5</f>
+        <v>34801.75</v>
+      </c>
+      <c r="I5" s="4">
+        <f>E5-H5</f>
+        <v>103010.75</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="4">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4">
+        <v>525</v>
+      </c>
+      <c r="D6" s="4">
+        <f>C6*1250</f>
+        <v>656250</v>
+      </c>
+      <c r="E6" s="4">
+        <f>D6*0.35</f>
+        <v>229687.5</v>
+      </c>
+      <c r="F6" s="4">
+        <v>17083</v>
+      </c>
+      <c r="G6" s="4">
+        <f>D6*0.30*0.15</f>
+        <v>29531.25</v>
+      </c>
+      <c r="H6" s="4">
+        <f>F6+G6</f>
+        <v>46614.25</v>
+      </c>
+      <c r="I6" s="4">
+        <f>E6-H6</f>
+        <v>183073.25</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4">
         <v>637.5</v>
       </c>
-      <c r="C6" s="4">
-        <v>1593750</v>
-      </c>
-      <c r="D6" s="4">
-        <f>C6*0.35</f>
-        <v>557812.5</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D7" s="4">
+        <f>C7*1250</f>
+        <v>796875</v>
+      </c>
+      <c r="E7" s="4">
+        <f>D7*0.35</f>
+        <v>278906.25</v>
+      </c>
+      <c r="F7" s="4">
         <v>17083</v>
       </c>
-      <c r="F6" s="4">
-        <f>C6*0.30*0.15</f>
-        <v>71718.75</v>
-      </c>
-      <c r="G6" s="4">
-        <f>E6+F6</f>
-        <v>88801.75</v>
-      </c>
-      <c r="H6" s="4">
-        <f>D6-G6</f>
-        <v>469010.75</v>
+      <c r="G7" s="4">
+        <f>D7*0.30*0.15</f>
+        <v>35859.38</v>
+      </c>
+      <c r="H7" s="4">
+        <f>F7+G7</f>
+        <v>52942.38</v>
+      </c>
+      <c r="I7" s="4">
+        <f>E7-H7</f>
+        <v>225963.87</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -726,7 +789,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -736,72 +799,72 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
